--- a/server/prisma/data/COLLEGES.xlsx
+++ b/server/prisma/data/COLLEGES.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="115">
   <si>
     <t>College</t>
   </si>
@@ -119,7 +119,7 @@
     <t>CA</t>
   </si>
   <si>
-    <t>Certificate in Agricultural Science (2nd year BSA)</t>
+    <t>Certificate in Agricultural Science (Associate Agriculture)</t>
   </si>
   <si>
     <t>Bachelor of Science in Agriculture (BSA)</t>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Bachelor of Science in Fisheries (BSF)</t>
+  </si>
+  <si>
+    <t>Bachelor of Science in Agricultural Extension</t>
   </si>
   <si>
     <t>CA - Libungan Campus</t>
@@ -554,7 +557,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,6 +590,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
@@ -838,7 +847,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -855,6 +864,47 @@
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -888,21 +938,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1028,7 +1063,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1040,120 +1075,121 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1172,8 +1208,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1184,36 +1226,39 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1692,7 +1737,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:B111"/>
+  <dimension ref="A2:B112"/>
   <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="24.1111111111111" customWidth="1"/>
@@ -1700,803 +1745,811 @@
   </cols>
   <sheetData>
     <row r="2" ht="13.2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="13.2" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" ht="13.2" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="13.2" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="13.2" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" ht="13.2" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" ht="13.2" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" ht="13.2" spans="1:2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" ht="13.2" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="13.2" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" ht="13.2" spans="1:2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" ht="13.2" spans="1:2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="13.2" spans="1:2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" ht="13.2" spans="1:2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="4" t="s">
+    <row r="16" ht="13.2" spans="1:2">
+      <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" ht="13.2" spans="1:2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" ht="13.2" spans="1:2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" ht="13.2" spans="1:2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
     </row>
     <row r="20" ht="13.2" spans="1:2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" ht="13.2" spans="1:2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
     </row>
     <row r="22" ht="13.2" spans="1:2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" ht="13.2" spans="1:2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" ht="13.2" spans="1:2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="25" ht="13.2" spans="1:2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" ht="13.2" spans="1:2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
     </row>
     <row r="27" ht="13.2" spans="1:2">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" ht="13.2" spans="1:2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" ht="13.2" spans="1:2">
-      <c r="A29" s="7" t="s">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" ht="13.2" spans="1:2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="7" t="s">
+    <row r="31" ht="13.2" spans="1:2">
+      <c r="A31" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" ht="13.2" spans="1:2">
-      <c r="A32" s="7" t="s">
+    <row r="32" ht="13.95" spans="1:2">
+      <c r="A32" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" ht="13.2" spans="1:2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" ht="13.2" spans="1:2">
-      <c r="A34" s="7" t="s">
+      <c r="A33" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="7" t="s">
+    </row>
+    <row r="34" s="1" customFormat="1" ht="13.2" spans="1:2">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+    </row>
+    <row r="35" ht="13.2" spans="1:2">
+      <c r="A35" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="35" ht="13.2" spans="1:2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+      <c r="B35" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="36" ht="13.2" spans="1:2">
-      <c r="A36" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" ht="13.2" spans="1:2">
+      <c r="A37" s="13" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="37" ht="13.2" spans="1:2">
-      <c r="A37" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="38" ht="13.2" spans="1:2">
-      <c r="A38" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="39" ht="13.2" spans="1:2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+      <c r="A39" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="40" ht="13.2" spans="1:2">
-      <c r="A40" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="10" t="s">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" ht="13.2" spans="1:2">
+      <c r="A41" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="41" ht="13.2" spans="1:2">
-      <c r="A41" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="42" ht="13.2" spans="1:2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+      <c r="A42" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="43" ht="13.2" spans="1:2">
-      <c r="A43" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="11" t="s">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" ht="13.2" spans="1:2">
+      <c r="A44" s="15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="44" ht="13.2" spans="1:2">
-      <c r="A44" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" ht="13.2" spans="1:2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+      <c r="A45" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="46" ht="13.2" spans="1:2">
-      <c r="A46" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="12" t="s">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+    </row>
+    <row r="47" ht="13.2" spans="1:2">
+      <c r="A47" s="16" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="47" ht="13.2" spans="1:2">
-      <c r="A47" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="48" ht="13.2" spans="1:2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
+      <c r="A48" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="49" ht="13.2" spans="1:2">
-      <c r="A49" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="12" t="s">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+    </row>
+    <row r="50" ht="13.2" spans="1:2">
+      <c r="A50" s="16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="50" ht="13.2" spans="1:2">
-      <c r="A50" s="12" t="s">
+      <c r="B50" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="12" t="s">
+    </row>
+    <row r="51" ht="13.2" spans="1:2">
+      <c r="A51" s="16" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="51" ht="13.2" spans="1:2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
+      <c r="B51" s="16" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="52" ht="13.2" spans="1:2">
-      <c r="A52" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+    </row>
+    <row r="53" ht="13.2" spans="1:2">
+      <c r="A53" s="18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="53" ht="13.2" spans="1:2">
-      <c r="A53" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="54" ht="13.2" spans="1:2">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
+      <c r="A54" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="55" ht="13.2" spans="1:2">
-      <c r="A55" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+    </row>
+    <row r="56" ht="13.2" spans="1:2">
+      <c r="A56" s="18" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="56" ht="13.2" spans="1:2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
+      <c r="B56" s="18" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="57" ht="13.2" spans="1:2">
-      <c r="A57" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="15" t="s">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" ht="13.2" spans="1:2">
+      <c r="A58" s="19" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="58" ht="13.2" spans="1:2">
-      <c r="A58" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="19" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="59" ht="13.2" spans="1:2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
+      <c r="A59" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="60" ht="13.2" spans="1:2">
-      <c r="A60" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="17" t="s">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+    </row>
+    <row r="61" ht="13.2" spans="1:2">
+      <c r="A61" s="21" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="61" ht="13.2" spans="1:2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
+      <c r="B61" s="21" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" ht="13.2" spans="1:2">
-      <c r="A62" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="13" t="s">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+    </row>
+    <row r="63" ht="13.2" spans="1:2">
+      <c r="A63" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="63" ht="13.2" spans="1:2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+      <c r="B63" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="64" ht="13.2" spans="1:2">
-      <c r="A64" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>66</v>
-      </c>
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" ht="13.2" spans="1:2">
-      <c r="A65" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" s="21" t="s">
+      <c r="A65" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="23" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="66" ht="13.2" spans="1:2">
-      <c r="A66" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="21" t="s">
+      <c r="A66" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="25" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="67" ht="13.2" spans="1:2">
-      <c r="A67" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="21" t="s">
+      <c r="A67" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="25" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="68" ht="13.2" spans="1:2">
-      <c r="A68" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="21" t="s">
+      <c r="A68" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="25" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="69" ht="13.2" spans="1:2">
-      <c r="A69" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69" s="21" t="s">
+      <c r="A69" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B69" s="25" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="70" ht="13.2" spans="1:2">
-      <c r="A70" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="21" t="s">
+      <c r="A70" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" s="25" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="71" ht="13.2" spans="1:2">
-      <c r="A71" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="21" t="s">
+      <c r="A71" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B71" s="25" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="72" ht="13.2" spans="1:2">
-      <c r="A72" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="21" t="s">
+      <c r="A72" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" s="25" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="73" ht="13.2" spans="1:2">
-      <c r="A73" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="21" t="s">
+      <c r="A73" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73" s="25" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="74" ht="13.2" spans="1:2">
-      <c r="A74" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="21" t="s">
+      <c r="A74" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" s="25" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="75" ht="13.2" spans="1:2">
-      <c r="A75" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="21" t="s">
+      <c r="A75" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" s="25" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="76" ht="13.2" spans="1:2">
-      <c r="A76" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B76" s="21" t="s">
+      <c r="A76" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76" s="25" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="77" ht="13.2" spans="1:2">
-      <c r="A77" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="21" t="s">
+      <c r="A77" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="25" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="78" ht="13.2" spans="1:2">
-      <c r="A78" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B78" s="21" t="s">
+      <c r="A78" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="25" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="79" ht="13.2" spans="1:2">
-      <c r="A79" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="21" t="s">
+      <c r="A79" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" s="25" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="80" ht="13.2" spans="1:2">
-      <c r="A80" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B80" s="21" t="s">
+      <c r="A80" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="25" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="81" ht="13.2" spans="1:2">
-      <c r="A81" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B81" s="21" t="s">
+      <c r="A81" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81" s="25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="82" ht="13.2" spans="1:2">
-      <c r="A82" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B82" s="21" t="s">
+      <c r="A82" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B82" s="25" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="83" ht="13.2" spans="1:2">
-      <c r="A83" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B83" s="21" t="s">
+      <c r="A83" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83" s="25" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="84" ht="13.2" spans="1:2">
-      <c r="A84" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B84" s="21" t="s">
+      <c r="A84" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" s="25" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="85" ht="13.2" spans="1:2">
-      <c r="A85" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B85" s="21" t="s">
+      <c r="A85" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B85" s="25" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="86" ht="13.2" spans="1:2">
-      <c r="A86" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B86" s="21" t="s">
+      <c r="A86" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B86" s="25" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="87" ht="13.2" spans="1:2">
-      <c r="A87" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B87" s="21" t="s">
+      <c r="A87" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" s="25" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="88" ht="13.2" spans="1:2">
-      <c r="A88" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B88" s="21" t="s">
+      <c r="A88" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" s="25" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="89" ht="13.2" spans="1:2">
-      <c r="A89" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B89" s="21" t="s">
+      <c r="A89" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" s="25" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="90" ht="13.2" spans="1:2">
-      <c r="A90" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B90" s="21" t="s">
+      <c r="A90" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="91" ht="13.2" spans="1:2">
-      <c r="A91" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B91" s="21" t="s">
+      <c r="A91" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" s="25" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="92" ht="13.2" spans="1:2">
-      <c r="A92" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B92" s="21" t="s">
+      <c r="A92" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B92" s="25" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="93" ht="13.2" spans="1:2">
-      <c r="A93" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B93" s="21" t="s">
+      <c r="A93" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93" s="25" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="94" ht="13.2" spans="1:2">
-      <c r="A94" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94" s="21" t="s">
+      <c r="A94" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B94" s="25" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="95" ht="13.2" spans="1:2">
-      <c r="A95" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B95" s="21" t="s">
+      <c r="A95" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B95" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="96" ht="13.2" spans="1:2">
-      <c r="A96" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B96" s="23" t="s">
+      <c r="A96" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B96" s="25" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="97" ht="13.2" spans="1:2">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
+      <c r="A97" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="98" ht="13.2" spans="1:2">
-      <c r="A98" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98" s="24" t="s">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" ht="13.2" spans="1:2">
+      <c r="A99" s="28" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="99" ht="13.2" spans="1:2">
-      <c r="A99" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B99" s="24" t="s">
+      <c r="B99" s="28" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B100" s="24" t="s">
+    <row r="100" ht="13.2" spans="1:2">
+      <c r="A100" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="101" ht="13.2" spans="1:2">
-      <c r="A101" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B101" s="24" t="s">
+      <c r="A101" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101" s="28" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="102" ht="13.2" spans="1:2">
-      <c r="A102" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B102" s="24" t="s">
+      <c r="A102" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B102" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="103" ht="13.2" spans="1:2">
-      <c r="A103" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B103" s="24" t="s">
+      <c r="A103" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B103" s="28" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="104" ht="13.2" spans="1:2">
-      <c r="A104" s="25"/>
-      <c r="B104" s="25"/>
+      <c r="A104" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B104" s="28" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="105" ht="13.2" spans="1:2">
-      <c r="A105" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B105" s="26" t="s">
+      <c r="A105" s="29"/>
+      <c r="B105" s="29"/>
+    </row>
+    <row r="106" ht="13.2" spans="1:2">
+      <c r="A106" s="30" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="106" ht="13.2" spans="1:2">
-      <c r="A106" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B106" s="26" t="s">
+      <c r="B106" s="30" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="107" ht="13.2" spans="1:2">
-      <c r="A107" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B107" s="26" t="s">
+      <c r="A107" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" s="30" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="108" ht="13.2" spans="1:2">
-      <c r="A108" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B108" s="26" t="s">
+      <c r="A108" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="30" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="109" ht="13.2" spans="1:2">
-      <c r="A109" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B109" s="26" t="s">
+      <c r="A109" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="30" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="110" ht="13.2" spans="1:2">
-      <c r="A110" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B110" s="26" t="s">
+      <c r="A110" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B110" s="30" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="111" ht="13.2" spans="1:2">
-      <c r="A111" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B111" s="26" t="s">
+      <c r="A111" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B111" s="30" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="112" ht="13.2" spans="1:2">
+      <c r="A112" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B112" s="30" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
